--- a/backend/data/financials_by_company/1668.HK.xlsx
+++ b/backend/data/financials_by_company/1668.HK.xlsx
@@ -652,140 +652,142 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>79399980</v>
+        <v>132302610</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-7143129000</v>
+        <v>1727800000</v>
       </c>
       <c r="E2" t="n">
-        <v>481212000</v>
+        <v>801834000</v>
       </c>
       <c r="F2" t="n">
-        <v>481212000</v>
+        <v>801834000</v>
       </c>
       <c r="G2" t="n">
-        <v>-8975762000</v>
+        <v>677640000</v>
       </c>
       <c r="H2" t="n">
-        <v>92141000</v>
+        <v>230544000</v>
       </c>
       <c r="I2" t="n">
-        <v>3317468000</v>
+        <v>6768284000</v>
       </c>
       <c r="J2" t="n">
-        <v>-6661917000</v>
+        <v>2529634000</v>
       </c>
       <c r="K2" t="n">
-        <v>-6754058000</v>
+        <v>2299090000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1508320000</v>
+        <v>-595344000</v>
       </c>
       <c r="M2" t="n">
-        <v>1522530000</v>
+        <v>787788000</v>
       </c>
       <c r="N2" t="n">
-        <v>14210000</v>
+        <v>192444000</v>
       </c>
       <c r="O2" t="n">
-        <v>-9377574020</v>
+        <v>8108610</v>
       </c>
       <c r="P2" t="n">
-        <v>-8975762000</v>
+        <v>760200000</v>
       </c>
       <c r="Q2" t="n">
-        <v>3945900000</v>
+        <v>8065551000</v>
       </c>
       <c r="R2" t="n">
-        <v>11441892848</v>
+        <v>8091892848</v>
       </c>
       <c r="S2" t="n">
-        <v>11441892848</v>
+        <v>8091892848</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7845</v>
+        <v>0.0939</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7845</v>
+        <v>0.0939</v>
       </c>
       <c r="V2" t="n">
-        <v>-8975762000</v>
+        <v>760200000</v>
       </c>
       <c r="W2" t="n">
-        <v>-8975762000</v>
+        <v>760200000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-8975762000</v>
+        <v>760200000</v>
       </c>
       <c r="Z2" t="n">
-        <v>142000</v>
+        <v>1076000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-8975904000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>759124000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>82560000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>-8975904000</v>
+        <v>676564000</v>
       </c>
       <c r="AD2" t="n">
-        <v>699316000</v>
+        <v>834738000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-8276588000</v>
+        <v>1511302000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-4903362000</v>
+        <v>-396208000</v>
       </c>
       <c r="AG2" t="n">
-        <v>446768000</v>
+        <v>829562000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-446768000</v>
+        <v>-829562000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1508320000</v>
+        <v>-595344000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1522530000</v>
+        <v>787788000</v>
       </c>
       <c r="AK2" t="n">
-        <v>14210000</v>
+        <v>192444000</v>
       </c>
       <c r="AL2" t="n">
-        <v>137480000</v>
+        <v>1550372000</v>
       </c>
       <c r="AM2" t="n">
-        <v>628432000</v>
+        <v>1297267000</v>
       </c>
       <c r="AN2" t="n">
-        <v>629251000</v>
+        <v>1351910000</v>
       </c>
       <c r="AO2" t="n">
-        <v>165652000</v>
+        <v>369156000</v>
       </c>
       <c r="AP2" t="n">
-        <v>463599000</v>
+        <v>982754000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>765912000</v>
+        <v>2847639000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3317468000</v>
+        <v>6768284000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4083380000</v>
+        <v>9615923000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4083380000</v>
+        <v>9615923000</v>
       </c>
     </row>
     <row r="3">
@@ -930,142 +932,140 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>132302610</v>
+        <v>79399980</v>
       </c>
       <c r="C4" t="n">
         <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>1727800000</v>
+        <v>-7143129000</v>
       </c>
       <c r="E4" t="n">
-        <v>801834000</v>
+        <v>481212000</v>
       </c>
       <c r="F4" t="n">
-        <v>801834000</v>
+        <v>481212000</v>
       </c>
       <c r="G4" t="n">
-        <v>677640000</v>
+        <v>-8975762000</v>
       </c>
       <c r="H4" t="n">
-        <v>230544000</v>
+        <v>92141000</v>
       </c>
       <c r="I4" t="n">
-        <v>6768284000</v>
+        <v>3317468000</v>
       </c>
       <c r="J4" t="n">
-        <v>2529634000</v>
+        <v>-6661917000</v>
       </c>
       <c r="K4" t="n">
-        <v>2299090000</v>
+        <v>-6754058000</v>
       </c>
       <c r="L4" t="n">
-        <v>-595344000</v>
+        <v>-1508320000</v>
       </c>
       <c r="M4" t="n">
-        <v>787788000</v>
+        <v>1522530000</v>
       </c>
       <c r="N4" t="n">
-        <v>192444000</v>
+        <v>14210000</v>
       </c>
       <c r="O4" t="n">
-        <v>8108610</v>
+        <v>-9377574020</v>
       </c>
       <c r="P4" t="n">
-        <v>760200000</v>
+        <v>-8975762000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8065551000</v>
+        <v>3945900000</v>
       </c>
       <c r="R4" t="n">
-        <v>8091892848</v>
+        <v>11441892848</v>
       </c>
       <c r="S4" t="n">
-        <v>8091892848</v>
+        <v>11441892848</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0939</v>
+        <v>-0.7845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0939</v>
+        <v>-0.7845</v>
       </c>
       <c r="V4" t="n">
-        <v>760200000</v>
+        <v>-8975762000</v>
       </c>
       <c r="W4" t="n">
-        <v>760200000</v>
+        <v>-8975762000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>760200000</v>
+        <v>-8975762000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1076000</v>
+        <v>142000</v>
       </c>
       <c r="AA4" t="n">
-        <v>759124000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>82560000</v>
-      </c>
+        <v>-8975904000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>676564000</v>
+        <v>-8975904000</v>
       </c>
       <c r="AD4" t="n">
-        <v>834738000</v>
+        <v>699316000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1511302000</v>
+        <v>-8276588000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-396208000</v>
+        <v>-4903362000</v>
       </c>
       <c r="AG4" t="n">
-        <v>829562000</v>
+        <v>446768000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-829562000</v>
+        <v>-446768000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-595344000</v>
+        <v>-1508320000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>787788000</v>
+        <v>1522530000</v>
       </c>
       <c r="AK4" t="n">
-        <v>192444000</v>
+        <v>14210000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1550372000</v>
+        <v>137480000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1297267000</v>
+        <v>628432000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1351910000</v>
+        <v>629251000</v>
       </c>
       <c r="AO4" t="n">
-        <v>369156000</v>
+        <v>165652000</v>
       </c>
       <c r="AP4" t="n">
-        <v>982754000</v>
+        <v>463599000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2847639000</v>
+        <v>765912000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6768284000</v>
+        <v>3317468000</v>
       </c>
       <c r="AS4" t="n">
-        <v>9615923000</v>
+        <v>4083380000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9615923000</v>
+        <v>4083380000</v>
       </c>
     </row>
   </sheetData>
@@ -1431,202 +1431,208 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>11441892848</v>
+        <v>8091892848</v>
       </c>
       <c r="C2" t="n">
-        <v>11441892848</v>
+        <v>8091892848</v>
       </c>
       <c r="D2" t="n">
-        <v>30179216000</v>
+        <v>34149203000</v>
       </c>
       <c r="E2" t="n">
-        <v>30223195000</v>
+        <v>35985234000</v>
       </c>
       <c r="F2" t="n">
-        <v>26592769000</v>
+        <v>45073744000</v>
       </c>
       <c r="G2" t="n">
-        <v>56813127000</v>
+        <v>81049120000</v>
       </c>
       <c r="H2" t="n">
-        <v>-2848124000</v>
+        <v>6426611000</v>
       </c>
       <c r="I2" t="n">
-        <v>26592769000</v>
+        <v>45073744000</v>
       </c>
       <c r="J2" t="n">
-        <v>2837000</v>
+        <v>9858000</v>
       </c>
       <c r="K2" t="n">
-        <v>26592769000</v>
+        <v>45073744000</v>
       </c>
       <c r="L2" t="n">
-        <v>38571848000</v>
+        <v>60299011000</v>
       </c>
       <c r="M2" t="n">
-        <v>26606950000</v>
+        <v>45089972000</v>
       </c>
       <c r="N2" t="n">
-        <v>14181000</v>
+        <v>16228000</v>
       </c>
       <c r="O2" t="n">
-        <v>26592769000</v>
+        <v>45073744000</v>
       </c>
       <c r="P2" t="n">
-        <v>4422000</v>
+        <v>48086000</v>
       </c>
       <c r="Q2" t="n">
         <v>286456000</v>
       </c>
       <c r="R2" t="n">
-        <v>18203556000</v>
+        <v>31089199000</v>
       </c>
       <c r="S2" t="n">
-        <v>9131812000</v>
+        <v>7222312000</v>
       </c>
       <c r="T2" t="n">
-        <v>9131812000</v>
+        <v>7222312000</v>
       </c>
       <c r="U2" t="n">
-        <v>60944475000</v>
+        <v>79297452000</v>
       </c>
       <c r="V2" t="n">
-        <v>19817537000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1037344000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>26291602000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>15413000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>6799625000</v>
+        <v>11050922000</v>
       </c>
       <c r="Z2" t="n">
-        <v>11980568000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1489000</v>
-      </c>
+        <v>15225267000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>11979079000</v>
+        <v>15225267000</v>
       </c>
       <c r="AC2" t="n">
-        <v>41126938000</v>
+        <v>53005850000</v>
       </c>
       <c r="AD2" t="n">
-        <v>18242627000</v>
+        <v>20759967000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1348000</v>
+        <v>9858000</v>
       </c>
       <c r="AF2" t="n">
-        <v>18241279000</v>
+        <v>20750109000</v>
       </c>
       <c r="AG2" t="n">
-        <v>15586139000</v>
+        <v>14381162000</v>
       </c>
       <c r="AH2" t="n">
-        <v>8953571000</v>
+        <v>3647999000</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>3707733000</v>
+        <v>4648572000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2924835000</v>
+        <v>6084591000</v>
       </c>
       <c r="AL2" t="n">
-        <v>87551425000</v>
+        <v>124387424000</v>
       </c>
       <c r="AM2" t="n">
-        <v>49272611000</v>
+        <v>64954963000</v>
       </c>
       <c r="AN2" t="n">
-        <v>926611000</v>
+        <v>3684246000</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>11000</v>
+        <v>3325000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11000</v>
+        <v>3325000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3996611000</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3996611000</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>43650433000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>59345317000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>684036000</v>
+        <v>1361317000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1076253000</v>
+        <v>-1143060000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1760289000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>2504377000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1361317000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>409019000</v>
+        <v>433114000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1057561000</v>
+        <v>1532318000</v>
       </c>
       <c r="BB2" t="n">
-        <v>293709000</v>
+        <v>538945000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>38278814000</v>
+        <v>59432461000</v>
       </c>
       <c r="BE2" t="n">
-        <v>83869000</v>
+        <v>258150000</v>
       </c>
       <c r="BF2" t="n">
-        <v>676590000</v>
+        <v>2854895000</v>
       </c>
       <c r="BG2" t="n">
-        <v>460578000</v>
+        <v>4269648000</v>
       </c>
       <c r="BH2" t="n">
-        <v>35562155000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+        <v>46880256000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>51353000</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>35562155000</v>
+        <v>46880256000</v>
       </c>
       <c r="BK2" t="n">
-        <v>949298000</v>
+        <v>5519728000</v>
       </c>
       <c r="BL2" t="n">
-        <v>505182000</v>
+        <v>2351409000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-304230000</v>
+        <v>-422163000</v>
       </c>
       <c r="BN2" t="n">
-        <v>809412000</v>
+        <v>2773572000</v>
       </c>
       <c r="BO2" t="n">
-        <v>41142000</v>
+        <v>1826173000</v>
       </c>
       <c r="BP2" t="n">
-        <v>41142000</v>
-      </c>
-      <c r="BQ2" t="inlineStr"/>
+        <v>1826173000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>271260000</v>
+      </c>
       <c r="BR2" t="n">
-        <v>41142000</v>
+        <v>1554913000</v>
       </c>
     </row>
     <row r="3">
@@ -1837,208 +1843,202 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>8091892848</v>
+        <v>11441892848</v>
       </c>
       <c r="C4" t="n">
-        <v>8091892848</v>
+        <v>11441892848</v>
       </c>
       <c r="D4" t="n">
-        <v>34149203000</v>
+        <v>30179216000</v>
       </c>
       <c r="E4" t="n">
-        <v>35985234000</v>
+        <v>30223195000</v>
       </c>
       <c r="F4" t="n">
-        <v>45073744000</v>
+        <v>26592769000</v>
       </c>
       <c r="G4" t="n">
-        <v>81049120000</v>
+        <v>56813127000</v>
       </c>
       <c r="H4" t="n">
-        <v>6426611000</v>
+        <v>-2848124000</v>
       </c>
       <c r="I4" t="n">
-        <v>45073744000</v>
+        <v>26592769000</v>
       </c>
       <c r="J4" t="n">
-        <v>9858000</v>
+        <v>2837000</v>
       </c>
       <c r="K4" t="n">
-        <v>45073744000</v>
+        <v>26592769000</v>
       </c>
       <c r="L4" t="n">
-        <v>60299011000</v>
+        <v>38571848000</v>
       </c>
       <c r="M4" t="n">
-        <v>45089972000</v>
+        <v>26606950000</v>
       </c>
       <c r="N4" t="n">
-        <v>16228000</v>
+        <v>14181000</v>
       </c>
       <c r="O4" t="n">
-        <v>45073744000</v>
+        <v>26592769000</v>
       </c>
       <c r="P4" t="n">
-        <v>48086000</v>
+        <v>4422000</v>
       </c>
       <c r="Q4" t="n">
         <v>286456000</v>
       </c>
       <c r="R4" t="n">
-        <v>31089199000</v>
+        <v>18203556000</v>
       </c>
       <c r="S4" t="n">
-        <v>7222312000</v>
+        <v>9131812000</v>
       </c>
       <c r="T4" t="n">
-        <v>7222312000</v>
+        <v>9131812000</v>
       </c>
       <c r="U4" t="n">
-        <v>79297452000</v>
+        <v>60944475000</v>
       </c>
       <c r="V4" t="n">
-        <v>26291602000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>15413000</v>
-      </c>
+        <v>19817537000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1037344000</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>11050922000</v>
+        <v>6799625000</v>
       </c>
       <c r="Z4" t="n">
-        <v>15225267000</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
+        <v>11980568000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1489000</v>
+      </c>
       <c r="AB4" t="n">
-        <v>15225267000</v>
+        <v>11979079000</v>
       </c>
       <c r="AC4" t="n">
-        <v>53005850000</v>
+        <v>41126938000</v>
       </c>
       <c r="AD4" t="n">
-        <v>20759967000</v>
+        <v>18242627000</v>
       </c>
       <c r="AE4" t="n">
-        <v>9858000</v>
+        <v>1348000</v>
       </c>
       <c r="AF4" t="n">
-        <v>20750109000</v>
+        <v>18241279000</v>
       </c>
       <c r="AG4" t="n">
-        <v>14381162000</v>
+        <v>15586139000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3647999000</v>
+        <v>8953571000</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>4648572000</v>
+        <v>3707733000</v>
       </c>
       <c r="AK4" t="n">
-        <v>6084591000</v>
+        <v>2924835000</v>
       </c>
       <c r="AL4" t="n">
-        <v>124387424000</v>
+        <v>87551425000</v>
       </c>
       <c r="AM4" t="n">
-        <v>64954963000</v>
+        <v>49272611000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3684246000</v>
+        <v>926611000</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>3325000</v>
+        <v>11000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3325000</v>
+        <v>11000</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>3996611000</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3996611000</v>
       </c>
       <c r="AT4" t="n">
-        <v>59345317000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>43650433000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>1361317000</v>
+        <v>684036000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-1143060000</v>
+        <v>-1076253000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2504377000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1361317000</v>
-      </c>
+        <v>1760289000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>433114000</v>
+        <v>409019000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1532318000</v>
+        <v>1057561000</v>
       </c>
       <c r="BB4" t="n">
-        <v>538945000</v>
+        <v>293709000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>59432461000</v>
+        <v>38278814000</v>
       </c>
       <c r="BE4" t="n">
-        <v>258150000</v>
+        <v>83869000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2854895000</v>
+        <v>676590000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4269648000</v>
+        <v>460578000</v>
       </c>
       <c r="BH4" t="n">
-        <v>46880256000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>51353000</v>
-      </c>
+        <v>35562155000</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>46880256000</v>
+        <v>35562155000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5519728000</v>
+        <v>949298000</v>
       </c>
       <c r="BL4" t="n">
-        <v>2351409000</v>
+        <v>505182000</v>
       </c>
       <c r="BM4" t="n">
-        <v>-422163000</v>
+        <v>-304230000</v>
       </c>
       <c r="BN4" t="n">
-        <v>2773572000</v>
+        <v>809412000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1826173000</v>
+        <v>41142000</v>
       </c>
       <c r="BP4" t="n">
-        <v>1826173000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>271260000</v>
-      </c>
+        <v>41142000</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
-        <v>1554913000</v>
+        <v>41142000</v>
       </c>
     </row>
   </sheetData>
@@ -2314,146 +2314,146 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44651</v>
       </c>
       <c r="B2" t="n">
-        <v>505546000</v>
+        <v>2551741000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1806114000</v>
+        <v>-11606458000</v>
       </c>
       <c r="D2" t="n">
-        <v>975817000</v>
+        <v>9590444000</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-2744000</v>
+        <v>-78257000</v>
       </c>
       <c r="G2" t="n">
-        <v>41142000</v>
+        <v>1554913000</v>
       </c>
       <c r="H2" t="n">
-        <v>230088000</v>
+        <v>3447947000</v>
       </c>
       <c r="I2" t="n">
-        <v>971000</v>
+        <v>168450000</v>
       </c>
       <c r="J2" t="n">
-        <v>-189917000</v>
+        <v>-2061484000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1425452000</v>
+        <v>-5152215000</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-592235000</v>
+        <v>-3064698000</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>-830297000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-2016014000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-14452000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-14452000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-830297000</v>
+        <v>-2001562000</v>
       </c>
       <c r="U2" t="n">
-        <v>-1806114000</v>
+        <v>-11592006000</v>
       </c>
       <c r="V2" t="n">
-        <v>975817000</v>
+        <v>9590444000</v>
       </c>
       <c r="W2" t="n">
-        <v>727245000</v>
+        <v>460733000</v>
       </c>
       <c r="X2" t="n">
-        <v>-4626000</v>
+        <v>93166000</v>
       </c>
       <c r="Y2" t="n">
-        <v>14210000</v>
+        <v>152266000</v>
       </c>
       <c r="Z2" t="n">
-        <v>5432000</v>
+        <v>105235000</v>
       </c>
       <c r="AA2" t="n">
-        <v>5432000</v>
+        <v>105235000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-33197000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>91286000</v>
-      </c>
+        <v>-53776000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-124483000</v>
+        <v>-53776000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1620000</v>
+        <v>34029000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1620000</v>
-      </c>
+        <v>34029000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>3742000</v>
+        <v>222979000</v>
       </c>
       <c r="AI2" t="n">
-        <v>6486000</v>
+        <v>301236000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2744000</v>
+        <v>-78257000</v>
       </c>
       <c r="AK2" t="n">
-        <v>508290000</v>
+        <v>2629998000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-25302000</v>
+        <v>-347710000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1084656000</v>
+        <v>1042003000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-504730000</v>
+        <v>1223571000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-434047000</v>
+        <v>720839000</v>
       </c>
       <c r="AP2" t="n">
-        <v>275282000</v>
+        <v>-772220000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1468645000</v>
+        <v>1890256000</v>
       </c>
       <c r="AR2" t="n">
-        <v>279506000</v>
+        <v>-2020443000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1386428000</v>
+        <v>596334000</v>
       </c>
       <c r="AT2" t="n">
-        <v>204000</v>
+        <v>6758000</v>
       </c>
       <c r="AU2" t="n">
-        <v>92141000</v>
+        <v>230544000</v>
       </c>
       <c r="AV2" t="n">
-        <v>92141000</v>
+        <v>230544000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2478590000</v>
+        <v>-120516000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-453000</v>
+        <v>-823280000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-6277000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-8276588000</v>
+        <v>1629860000</v>
       </c>
     </row>
     <row r="3">
@@ -2612,146 +2612,146 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44651</v>
+        <v>45657</v>
       </c>
       <c r="B4" t="n">
-        <v>2551741000</v>
+        <v>505546000</v>
       </c>
       <c r="C4" t="n">
-        <v>-11606458000</v>
+        <v>-1806114000</v>
       </c>
       <c r="D4" t="n">
-        <v>9590444000</v>
+        <v>975817000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-78257000</v>
+        <v>-2744000</v>
       </c>
       <c r="G4" t="n">
-        <v>1554913000</v>
+        <v>41142000</v>
       </c>
       <c r="H4" t="n">
-        <v>3447947000</v>
+        <v>230088000</v>
       </c>
       <c r="I4" t="n">
-        <v>168450000</v>
+        <v>971000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2061484000</v>
+        <v>-189917000</v>
       </c>
       <c r="K4" t="n">
-        <v>-5152215000</v>
+        <v>-1425452000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-3064698000</v>
+        <v>-592235000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-2016014000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-14452000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-14452000</v>
-      </c>
+        <v>-830297000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-2001562000</v>
+        <v>-830297000</v>
       </c>
       <c r="U4" t="n">
-        <v>-11592006000</v>
+        <v>-1806114000</v>
       </c>
       <c r="V4" t="n">
-        <v>9590444000</v>
+        <v>975817000</v>
       </c>
       <c r="W4" t="n">
-        <v>460733000</v>
+        <v>727245000</v>
       </c>
       <c r="X4" t="n">
-        <v>93166000</v>
+        <v>-4626000</v>
       </c>
       <c r="Y4" t="n">
-        <v>152266000</v>
+        <v>14210000</v>
       </c>
       <c r="Z4" t="n">
-        <v>105235000</v>
+        <v>5432000</v>
       </c>
       <c r="AA4" t="n">
-        <v>105235000</v>
+        <v>5432000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-53776000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>-33197000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>91286000</v>
+      </c>
       <c r="AD4" t="n">
-        <v>-53776000</v>
+        <v>-124483000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34029000</v>
+        <v>-1620000</v>
       </c>
       <c r="AF4" t="n">
-        <v>34029000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1620000</v>
+      </c>
       <c r="AH4" t="n">
-        <v>222979000</v>
+        <v>3742000</v>
       </c>
       <c r="AI4" t="n">
-        <v>301236000</v>
+        <v>6486000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-78257000</v>
+        <v>-2744000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2629998000</v>
+        <v>508290000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-347710000</v>
+        <v>-25302000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1042003000</v>
+        <v>1084656000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1223571000</v>
+        <v>-504730000</v>
       </c>
       <c r="AO4" t="n">
-        <v>720839000</v>
+        <v>-434047000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-772220000</v>
+        <v>275282000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1890256000</v>
+        <v>1468645000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2020443000</v>
+        <v>279506000</v>
       </c>
       <c r="AS4" t="n">
-        <v>596334000</v>
+        <v>1386428000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6758000</v>
+        <v>204000</v>
       </c>
       <c r="AU4" t="n">
-        <v>230544000</v>
+        <v>92141000</v>
       </c>
       <c r="AV4" t="n">
-        <v>230544000</v>
+        <v>92141000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-120516000</v>
+        <v>2478590000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-823280000</v>
+        <v>-453000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-6277000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1629860000</v>
+        <v>-8276588000</v>
       </c>
     </row>
   </sheetData>
@@ -3336,192 +3336,192 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EV1" t="inlineStr">
@@ -3625,7 +3625,7 @@
         <v>10</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -3680,7 +3680,7 @@
         <v>4.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="AN2" t="n">
         <v>1.5285715</v>
@@ -3813,10 +3813,10 @@
         <v>-53.188</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.08547008</v>
+        <v>0.009433985000000001</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CF2" t="n">
         <v>0.02</v>
@@ -3926,143 +3926,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>China South City Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>CHINASOUTHCITY</t>
-        </is>
+      <c r="DJ2" t="n">
+        <v>-1.8348594</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.107</v>
       </c>
       <c r="DL2" t="n">
-        <v>-1.8348594</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.107</v>
+        <v>-0.0019999966</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>0.107 - 0.11</t>
+        </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>HKSE</t>
         </is>
       </c>
       <c r="DO2" t="n">
-        <v>1754880849</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>finmb_60367754</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.002000004</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.019047659</v>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+          <t>0.105 - 0.132</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.024999999</v>
       </c>
       <c r="DT2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DV2" t="b">
+        <v>-0.18939392</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.9433985</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1745915803</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1745915803</v>
+      </c>
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="b">
+      <c r="DY2" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="EA2" t="n">
         <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1254274200000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0019999966</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.107 - 0.11</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.002000004</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.019047659</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.105 - 0.132</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>15</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.024999999</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.18939392</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-8.5470085</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1745915803</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1745915803</v>
+        <v>15</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>CHINASOUTHCITY</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>China South City Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EK2" t="b">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.07000000000000001</v>
+        <v>1254274200000</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EN2" t="n">
+        <v>1754880849</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>finmb_60367754</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="ES2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EU2" t="b">
         <v>0</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
       </c>
       <c r="EV2" t="inlineStr"/>
     </row>
